--- a/results/log_pv_cap/log_pv_cap_densities_hdensity_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_hdensity_effects.xlsx
@@ -511,32 +511,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hdensity</t>
+          <t>D(Households)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.327</t>
+          <t>-0.074</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.335</t>
+          <t>-0.078</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -546,353 +546,353 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>-0.002</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.925</t>
+          <t>7.240</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.598</t>
+          <t>-0.089</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.523</t>
+          <t>7.328</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>5.381</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.376</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5.005</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.133</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.560</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>4.573</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-0.136</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>4.709</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.404</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.043</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.361</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-2.290</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.427</t>
+          <t>1.072</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-1.863</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.122</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>3.809</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.453</t>
+          <t>4.334</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.813</t>
+          <t>4.196</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>-0.249</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.240</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.832</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.855</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.937</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.077</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.028</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.364</t>
+          <t>-0.358</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.038</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.369</t>
+          <t>-0.321</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.159</t>
+          <t>-0.208</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.124</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.085</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.237</t>
+          <t>-0.266</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.212</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.131</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>-0.079</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.052</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-0.139</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-0.127</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-0.133</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-0.129</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>-0.004</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.019</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.105</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.068</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.036</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-0.091</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-0.074</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.017</t>
         </is>
       </c>
     </row>
